--- a/DataFiles/DetailsFileTesting.xlsx
+++ b/DataFiles/DetailsFileTesting.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="17925" windowHeight="9645"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="22935" windowHeight="9645"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="84">
   <si>
     <t>Varibles</t>
   </si>
@@ -154,21 +154,6 @@
     <t>d1st04v10</t>
   </si>
   <si>
-    <t>BG-MA by attribute for extend-20.02.2026_073455</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_20.02.2026_073455</t>
-  </si>
-  <si>
-    <t>BG_Resource_20.02.2026_073455</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_20.02.2026_073455</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_21.02.2026_073455</t>
-  </si>
-  <si>
     <t>D1ST04R02</t>
   </si>
   <si>
@@ -193,19 +178,97 @@
     <t>D1ST05M01</t>
   </si>
   <si>
-    <t>BG-MA by attribute for extend-20.02.2026_125032</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_20.02.2026_125032</t>
-  </si>
-  <si>
-    <t>BG_Resource_20.02.2026_125032</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_20.02.2026_125032</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_21.02.2026_125032</t>
+    <t>SearWordForDelete</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>SearWordForDeleteTemplate</t>
+  </si>
+  <si>
+    <t>BG_AT by</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-27.03.2026_111805</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_27.03.2026_111805</t>
+  </si>
+  <si>
+    <t>BG_Resource_27.03.2026_111805</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_27.03.2026_111805</t>
+  </si>
+  <si>
+    <t>newApiAlarmForMessage</t>
+  </si>
+  <si>
+    <t>BG- New APi ex st 06 from 07 LP</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_31.03.2026_131150</t>
+  </si>
+  <si>
+    <t>apiAlarmNameForEsclationAlarm</t>
+  </si>
+  <si>
+    <t>New APi St 06 esc</t>
+  </si>
+  <si>
+    <t>manualAlarmNameForEsclationAlarm</t>
+  </si>
+  <si>
+    <t>BG-MA by Esc resource MS</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-31.03.2026_095526</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_31.03.2026_095526</t>
+  </si>
+  <si>
+    <t>BG_Resource_31.03.2026_095526</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-31.03.2026_102648</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_31.03.2026_102648</t>
+  </si>
+  <si>
+    <t>BG_Resource_31.03.2026_102648</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_31.03.2026_102648</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_01.04.2026_143055</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-01.04.2026_154609</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-01.04.2026_155052</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-04.04.2026_130527</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_04.04.2026_130527</t>
+  </si>
+  <si>
+    <t>BG_Resource_04.04.2026_130527</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_04.04.2026_130527</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_05.04.2026_130527</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-06.04.2026_074008</t>
   </si>
 </sst>
 </file>
@@ -213,7 +276,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,6 +295,12 @@
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2A00FF"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -258,13 +327,14 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -560,10 +630,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="1" max="1" customWidth="true" width="36.0"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="69.5703125"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="52.140625"/>
     <col min="4" max="4" customWidth="true" width="38.7109375"/>
@@ -657,7 +727,7 @@
         <v>20</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -665,7 +735,7 @@
         <v>21</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E12" s="2"/>
     </row>
@@ -734,18 +804,18 @@
         <v>36</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="B21" t="s" s="0">
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s" s="0">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -770,23 +840,23 @@
     </row>
     <row r="25">
       <c r="B25" t="s" s="0">
-        <v>61</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s" s="0">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s" s="0">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -795,20 +865,20 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s" s="0">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s" s="0">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s" s="0">
-        <v>58</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -827,8 +897,49 @@
         <v>42</v>
       </c>
     </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/DataFiles/DetailsFileTesting.xlsx
+++ b/DataFiles/DetailsFileTesting.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="99">
   <si>
     <t>Varibles</t>
   </si>
@@ -269,6 +269,51 @@
   </si>
   <si>
     <t>BG-MA by attribute for extend-06.04.2026_074008</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-13.04.2026_144433</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_13.04.2026_144433</t>
+  </si>
+  <si>
+    <t>BG_Resource_13.04.2026_144433</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_13.04.2026_144433</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_14.04.2026_144433</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-23.04.2026_131534</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_23.04.2026_131534</t>
+  </si>
+  <si>
+    <t>BG_Resource_23.04.2026_131534</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_23.04.2026_131534</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_24.04.2026_131534</t>
+  </si>
+  <si>
+    <t>BG-MA by attribute for extend-27.04.2026_110900</t>
+  </si>
+  <si>
+    <t>BG_AT by Atrribute_27.04.2026_110900</t>
+  </si>
+  <si>
+    <t>BG_Resource_27.04.2026_110900</t>
+  </si>
+  <si>
+    <t>BG_Escaltion Resource_27.04.2026_110900</t>
+  </si>
+  <si>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_28.04.2026_110900</t>
   </si>
 </sst>
 </file>
@@ -810,12 +855,12 @@
     </row>
     <row r="21">
       <c r="B21" t="s" s="0">
-        <v>79</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s" s="0">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -840,7 +885,7 @@
     </row>
     <row r="25">
       <c r="B25" t="s" s="0">
-        <v>81</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -873,12 +918,12 @@
     </row>
     <row r="29">
       <c r="B29" t="s" s="0">
-        <v>82</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s" s="0">
-        <v>83</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:6">

--- a/DataFiles/DetailsFileTesting.xlsx
+++ b/DataFiles/DetailsFileTesting.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="22935" windowHeight="9645"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="22605" windowHeight="9645"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
   <si>
     <t>Varibles</t>
   </si>
@@ -190,27 +190,12 @@
     <t>BG_AT by</t>
   </si>
   <si>
-    <t>BG-MA by attribute for extend-27.03.2026_111805</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_27.03.2026_111805</t>
-  </si>
-  <si>
-    <t>BG_Resource_27.03.2026_111805</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_27.03.2026_111805</t>
-  </si>
-  <si>
     <t>newApiAlarmForMessage</t>
   </si>
   <si>
     <t>BG- New APi ex st 06 from 07 LP</t>
   </si>
   <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_31.03.2026_131150</t>
-  </si>
-  <si>
     <t>apiAlarmNameForEsclationAlarm</t>
   </si>
   <si>
@@ -223,84 +208,6 @@
     <t>BG-MA by Esc resource MS</t>
   </si>
   <si>
-    <t>BG-MA by attribute for extend-31.03.2026_095526</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_31.03.2026_095526</t>
-  </si>
-  <si>
-    <t>BG_Resource_31.03.2026_095526</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-31.03.2026_102648</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_31.03.2026_102648</t>
-  </si>
-  <si>
-    <t>BG_Resource_31.03.2026_102648</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_31.03.2026_102648</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_01.04.2026_143055</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-01.04.2026_154609</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-01.04.2026_155052</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-04.04.2026_130527</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_04.04.2026_130527</t>
-  </si>
-  <si>
-    <t>BG_Resource_04.04.2026_130527</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_04.04.2026_130527</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_05.04.2026_130527</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-06.04.2026_074008</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-13.04.2026_144433</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_13.04.2026_144433</t>
-  </si>
-  <si>
-    <t>BG_Resource_13.04.2026_144433</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_13.04.2026_144433</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_14.04.2026_144433</t>
-  </si>
-  <si>
-    <t>BG-MA by attribute for extend-23.04.2026_131534</t>
-  </si>
-  <si>
-    <t>BG_AT by Atrribute_23.04.2026_131534</t>
-  </si>
-  <si>
-    <t>BG_Resource_23.04.2026_131534</t>
-  </si>
-  <si>
-    <t>BG_Escaltion Resource_23.04.2026_131534</t>
-  </si>
-  <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_24.04.2026_131534</t>
-  </si>
-  <si>
     <t>BG-MA by attribute for extend-27.04.2026_110900</t>
   </si>
   <si>
@@ -313,15 +220,35 @@
     <t>BG_Escaltion Resource_27.04.2026_110900</t>
   </si>
   <si>
-    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_28.04.2026_110900</t>
+    <t>Bg_1 Day Information-Event by Fire fighter (two Station)_02.05.2026_095310</t>
+  </si>
+  <si>
+    <t>st01FFEmailCallSms</t>
+  </si>
+  <si>
+    <t>Jonas4 Jonas04</t>
+  </si>
+  <si>
+    <t>ChatGroupByAttribute</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>fdsf</t>
+  </si>
+  <si>
+    <t>sdfsdf</t>
+  </si>
+  <si>
+    <t>sff</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,6 +273,14 @@
       <color rgb="FF2A00FF"/>
       <name val="Courier New"/>
       <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -372,7 +307,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
@@ -380,6 +315,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -675,232 +611,232 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="36.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="69.5703125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="52.140625"/>
-    <col min="4" max="4" customWidth="true" width="38.7109375"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="47.140625"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="69.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.7109375" customWidth="1"/>
+    <col min="5" max="5" width="47.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" t="s" s="0">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" t="s" s="0">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="s" s="0">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" t="s" s="0">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" t="s" s="0">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" t="s" s="0">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" t="s" s="0">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="B10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" t="s" s="0">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="B11" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" t="s" s="0">
+      <c r="A12" t="s">
         <v>21</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="B12" t="s">
         <v>46</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" t="s" s="0">
+      <c r="A13" t="s">
         <v>22</v>
       </c>
-      <c r="B13" t="s" s="0">
+      <c r="B13" t="s">
         <v>23</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" t="s" s="0">
+      <c r="A14" t="s">
         <v>24</v>
       </c>
-      <c r="B14" t="s" s="0">
+      <c r="B14" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" t="s" s="0">
+      <c r="A15" t="s">
         <v>26</v>
       </c>
-      <c r="B15" t="s" s="0">
+      <c r="B15" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" t="s" s="0">
+      <c r="A16" t="s">
         <v>28</v>
       </c>
-      <c r="B16" t="s" s="0">
+      <c r="B16" t="s">
         <v>29</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" t="s" s="0">
+      <c r="A17" t="s">
         <v>30</v>
       </c>
-      <c r="B17" t="s" s="0">
+      <c r="B17" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" t="s" s="0">
+      <c r="A18" t="s">
         <v>32</v>
       </c>
-      <c r="B18" t="s" s="0">
+      <c r="B18" t="s">
         <v>33</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" t="s" s="0">
+      <c r="A19" t="s">
         <v>34</v>
       </c>
-      <c r="B19" t="s" s="0">
+      <c r="B19" t="s">
         <v>35</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" t="s" s="0">
+      <c r="A20" t="s">
         <v>36</v>
       </c>
-      <c r="B20" t="s" s="0">
+      <c r="B20" t="s">
         <v>46</v>
       </c>
       <c r="E20" s="2"/>
     </row>
-    <row r="21">
-      <c r="B21" t="s" s="0">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="s" s="0">
-        <v>96</v>
+    <row r="21" spans="1:6">
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" t="s" s="0">
+      <c r="A23" t="s">
         <v>37</v>
       </c>
-      <c r="B23" t="s" s="0">
+      <c r="B23" t="s">
         <v>43</v>
       </c>
       <c r="C23" s="2"/>
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" t="s" s="0">
+      <c r="A24" t="s">
         <v>38</v>
       </c>
-      <c r="B24" t="s" s="0">
+      <c r="B24" t="s">
         <v>44</v>
       </c>
       <c r="C24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25">
-      <c r="B25" t="s" s="0">
-        <v>97</v>
+    <row r="25" spans="1:6">
+      <c r="B25" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" t="s" s="0">
+      <c r="A26" t="s">
         <v>47</v>
       </c>
-      <c r="B26" t="s" s="0">
+      <c r="B26" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" t="s" s="0">
+      <c r="A27" t="s">
         <v>49</v>
       </c>
-      <c r="B27" t="s" s="0">
+      <c r="B27" t="s">
         <v>50</v>
       </c>
       <c r="C27" s="3"/>
@@ -909,77 +845,108 @@
       <c r="F27" s="3"/>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" t="s" s="0">
+      <c r="A28" t="s">
         <v>51</v>
       </c>
-      <c r="B28" t="s" s="0">
+      <c r="B28" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" t="s" s="0">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="s" s="0">
-        <v>94</v>
+    <row r="29" spans="1:6">
+      <c r="B29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="B30" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" t="s" s="0">
+      <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="B31" t="s" s="0">
+      <c r="B31" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" t="s" s="0">
+      <c r="A32" t="s">
         <v>41</v>
       </c>
-      <c r="B32" t="s" s="0">
+      <c r="B32" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" t="s" s="0">
+      <c r="A33" t="s">
         <v>53</v>
       </c>
-      <c r="B33" t="s" s="0">
+      <c r="B33" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" t="s" s="0">
+      <c r="A34" t="s">
         <v>55</v>
       </c>
-      <c r="B34" t="s" s="0">
+      <c r="B34" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" t="s" s="0">
+      <c r="A35" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
         <v>61</v>
       </c>
-      <c r="B35" t="s" s="0">
+      <c r="B37" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s" s="0">
-        <v>64</v>
-      </c>
-      <c r="B36" t="s" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s" s="0">
-        <v>66</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>67</v>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="B40" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="B41" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="B42" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
